--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.62223041937387</v>
+        <v>5.301112443148254</v>
       </c>
       <c r="D2" t="n">
-        <v>32.91517962530551</v>
+        <v>5.348716689112146</v>
       </c>
       <c r="E2" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F2" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.58422761466328</v>
+        <v>3.507436987382782</v>
       </c>
       <c r="D3" t="n">
-        <v>21.76201629605428</v>
+        <v>3.53632764810882</v>
       </c>
       <c r="E3" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F3" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.87631520058648</v>
+        <v>5.829901220095303</v>
       </c>
       <c r="D4" t="n">
-        <v>36.35273612823241</v>
+        <v>5.907319620837766</v>
       </c>
       <c r="E4" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F4" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.63198352801061</v>
+        <v>4.002697323301724</v>
       </c>
       <c r="D5" t="n">
-        <v>26.17097506928732</v>
+        <v>4.25278344875919</v>
       </c>
       <c r="E5" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F5" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.957725988101</v>
+        <v>6.655630473066413</v>
       </c>
       <c r="D6" t="n">
-        <v>23.75348138226854</v>
+        <v>3.859940724618637</v>
       </c>
       <c r="E6" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F6" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.01127311803048</v>
+        <v>6.826831881679953</v>
       </c>
       <c r="D7" t="n">
-        <v>41.2903186617481</v>
+        <v>6.709676782534067</v>
       </c>
       <c r="E7" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F7" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.48399464442473</v>
+        <v>3.978649129719019</v>
       </c>
       <c r="D8" t="n">
-        <v>23.03571373611564</v>
+        <v>3.743303482118792</v>
       </c>
       <c r="E8" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F8" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.02198371854331</v>
+        <v>4.228572354263288</v>
       </c>
       <c r="D9" t="n">
-        <v>23.4803694649445</v>
+        <v>3.815560038053481</v>
       </c>
       <c r="E9" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F9" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>55.62288801409252</v>
+        <v>9.038719302290035</v>
       </c>
       <c r="D10" t="n">
-        <v>53.8467302871189</v>
+        <v>8.750093671656822</v>
       </c>
       <c r="E10" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F10" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.03825509872781</v>
+        <v>2.768716453543269</v>
       </c>
       <c r="D11" t="n">
-        <v>18.30614115266401</v>
+        <v>2.974747937307901</v>
       </c>
       <c r="E11" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F11" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.54367275432895</v>
+        <v>6.750846822578453</v>
       </c>
       <c r="D12" t="n">
-        <v>40.64480358015165</v>
+        <v>6.604780581774643</v>
       </c>
       <c r="E12" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F12" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.16371371507277</v>
+        <v>7.014103478699326</v>
       </c>
       <c r="D13" t="n">
-        <v>44.61507122554507</v>
+        <v>7.249949074151074</v>
       </c>
       <c r="E13" t="n">
-        <v>10.83880904479139</v>
+        <v>1.761306469778602</v>
       </c>
       <c r="F13" t="n">
-        <v>10.66190917558988</v>
+        <v>1.732560241033356</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
